--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 17:52 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:12 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:12 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:15 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:15 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:30 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:30 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:48 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:48 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:54 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 19:54 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 20:43 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 20:43 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 20:49 ET.</t>
         </is>
       </c>
     </row>

--- a/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
+++ b/mstr-valuation/TON618_MSTR_Valuation_Model.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 20:49 ET.</t>
+          <t>NAV / sum-of-the-parts. Edit the shaded input cells; outputs recompute. Seeded 28 Jun 2026, 20:57 ET.</t>
         </is>
       </c>
     </row>
